--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0002T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.19305778861797</v>
+        <v>6.206371890650421</v>
       </c>
       <c r="D2" t="n">
-        <v>38.62463933456365</v>
+        <v>6.276503891866594</v>
       </c>
       <c r="E2" t="n">
-        <v>14.35024125608943</v>
+        <v>2.331914204114533</v>
       </c>
       <c r="F2" t="n">
-        <v>14.34358224712914</v>
+        <v>2.330832115158485</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.77491338832539</v>
+        <v>10.20092342560288</v>
       </c>
       <c r="D3" t="n">
-        <v>63.69538904602675</v>
+        <v>10.35050071997935</v>
       </c>
       <c r="E3" t="n">
-        <v>14.35024125608943</v>
+        <v>2.331914204114533</v>
       </c>
       <c r="F3" t="n">
-        <v>14.34358224712914</v>
+        <v>2.330832115158485</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.98870493034677</v>
+        <v>2.27316455118135</v>
       </c>
       <c r="D4" t="n">
-        <v>13.62459254084422</v>
+        <v>2.213996287887185</v>
       </c>
       <c r="E4" t="n">
-        <v>14.35024125608943</v>
+        <v>2.331914204114533</v>
       </c>
       <c r="F4" t="n">
-        <v>14.34358224712914</v>
+        <v>2.330832115158485</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.0461616543561</v>
+        <v>5.857501268832866</v>
       </c>
       <c r="D5" t="n">
-        <v>35.85735959445957</v>
+        <v>5.82682093409968</v>
       </c>
       <c r="E5" t="n">
-        <v>14.35024125608943</v>
+        <v>2.331914204114533</v>
       </c>
       <c r="F5" t="n">
-        <v>14.34358224712914</v>
+        <v>2.330832115158485</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.21133524659129</v>
+        <v>2.634341977571085</v>
       </c>
       <c r="D6" t="n">
-        <v>16.90422359475723</v>
+        <v>2.74693633414805</v>
       </c>
       <c r="E6" t="n">
-        <v>14.35024125608943</v>
+        <v>2.331914204114533</v>
       </c>
       <c r="F6" t="n">
-        <v>14.34358224712914</v>
+        <v>2.330832115158485</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.45042575201133</v>
+        <v>7.710694184701841</v>
       </c>
       <c r="D7" t="n">
-        <v>47.15954921042135</v>
+        <v>7.66342674669347</v>
       </c>
       <c r="E7" t="n">
-        <v>14.35024125608943</v>
+        <v>2.331914204114533</v>
       </c>
       <c r="F7" t="n">
-        <v>14.34358224712914</v>
+        <v>2.330832115158485</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>54.16361497334413</v>
+        <v>8.801587433168422</v>
       </c>
       <c r="D8" t="n">
-        <v>53.57989042946016</v>
+        <v>8.706732194787277</v>
       </c>
       <c r="E8" t="n">
-        <v>14.35024125608943</v>
+        <v>2.331914204114533</v>
       </c>
       <c r="F8" t="n">
-        <v>14.34358224712914</v>
+        <v>2.330832115158485</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.00361561251457</v>
+        <v>6.500587537033618</v>
       </c>
       <c r="D9" t="n">
-        <v>39.99911438642471</v>
+        <v>6.499856087794015</v>
       </c>
       <c r="E9" t="n">
-        <v>14.35024125608943</v>
+        <v>2.331914204114533</v>
       </c>
       <c r="F9" t="n">
-        <v>14.34358224712914</v>
+        <v>2.330832115158485</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>54.5406630821162</v>
+        <v>8.862857750843883</v>
       </c>
       <c r="D10" t="n">
-        <v>53.81193066462179</v>
+        <v>8.744438733001042</v>
       </c>
       <c r="E10" t="n">
-        <v>14.35024125608943</v>
+        <v>2.331914204114533</v>
       </c>
       <c r="F10" t="n">
-        <v>14.34358224712914</v>
+        <v>2.330832115158485</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.94714539867017</v>
+        <v>6.328911127283903</v>
       </c>
       <c r="D11" t="n">
-        <v>38.03942876811487</v>
+        <v>6.181407174818667</v>
       </c>
       <c r="E11" t="n">
-        <v>14.35024125608943</v>
+        <v>2.331914204114533</v>
       </c>
       <c r="F11" t="n">
-        <v>14.34358224712914</v>
+        <v>2.330832115158485</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.90470178868026</v>
+        <v>5.834514040660542</v>
       </c>
       <c r="D12" t="n">
-        <v>35.05588389728842</v>
+        <v>5.696581133309369</v>
       </c>
       <c r="E12" t="n">
-        <v>14.35024125608943</v>
+        <v>2.331914204114533</v>
       </c>
       <c r="F12" t="n">
-        <v>14.34358224712914</v>
+        <v>2.330832115158485</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
